--- a/artfynd/A 37488-2023 artfynd.xlsx
+++ b/artfynd/A 37488-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37488-2023 artfynd.xlsx
+++ b/artfynd/A 37488-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AY97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112724304</v>
+        <v>112728863</v>
       </c>
       <c r="B2" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Storhammartjärn, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596460</v>
+        <v>596367</v>
       </c>
       <c r="R2" t="n">
-        <v>7050313</v>
+        <v>7050435</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,19 +743,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112728862</v>
+        <v>112727894</v>
       </c>
       <c r="B3" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,38 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storhammartjärn, Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596362</v>
+        <v>596428</v>
       </c>
       <c r="R3" t="n">
-        <v>7050462</v>
+        <v>7050348</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -886,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112721816</v>
+        <v>112727895</v>
       </c>
       <c r="B4" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,42 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596388</v>
+        <v>596597</v>
       </c>
       <c r="R4" t="n">
-        <v>7050401</v>
+        <v>7050432</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,19 +937,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112724722</v>
+        <v>112727896</v>
       </c>
       <c r="B5" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,42 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596494</v>
+        <v>596520</v>
       </c>
       <c r="R5" t="n">
-        <v>7050406</v>
+        <v>7050456</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,19 +1034,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112727889</v>
+        <v>112727897</v>
       </c>
       <c r="B6" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,38 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596559</v>
+        <v>596283</v>
       </c>
       <c r="R6" t="n">
-        <v>7050308</v>
+        <v>7050426</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1238,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112727871</v>
+        <v>112721501</v>
       </c>
       <c r="B7" t="n">
-        <v>56761</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,42 +1171,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596547</v>
+        <v>596275</v>
       </c>
       <c r="R7" t="n">
-        <v>7050464</v>
+        <v>7050381</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,9 +1229,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,27 +1256,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112728859</v>
+        <v>112722014</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,19 +1297,20 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storhammartjärn, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596345</v>
+        <v>596386</v>
       </c>
       <c r="R8" t="n">
-        <v>7050466</v>
+        <v>7050495</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,9 +1337,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,27 +1364,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112727876</v>
+        <v>112722145</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,19 +1405,20 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596457</v>
+        <v>596454</v>
       </c>
       <c r="R9" t="n">
-        <v>7050320</v>
+        <v>7050541</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,9 +1445,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,65 +1472,61 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112727872</v>
+        <v>112722311</v>
       </c>
       <c r="B10" t="n">
-        <v>96091</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596466</v>
+        <v>596458</v>
       </c>
       <c r="R10" t="n">
-        <v>7050465</v>
+        <v>7050507</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1622,9 +1553,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,67 +1580,58 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112723822</v>
+        <v>112722480</v>
       </c>
       <c r="B11" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596600</v>
+        <v>596498</v>
       </c>
       <c r="R11" t="n">
-        <v>7050366</v>
+        <v>7050530</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1731,7 +1663,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1741,7 +1673,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,27 +1688,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112722014</v>
+        <v>112722495</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,14 +1732,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596386</v>
+        <v>596516</v>
       </c>
       <c r="R12" t="n">
-        <v>7050496</v>
+        <v>7050477</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1844,7 +1771,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1781,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,65 +1796,61 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112727899</v>
+        <v>112722575</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596631</v>
+        <v>596528</v>
       </c>
       <c r="R13" t="n">
-        <v>7050393</v>
+        <v>7050493</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1954,9 +1877,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1971,27 +1904,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112728854</v>
+        <v>112722641</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,19 +1945,20 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storhammartjärn, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596336</v>
+        <v>596550</v>
       </c>
       <c r="R14" t="n">
-        <v>7050376</v>
+        <v>7050491</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2056,9 +1985,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,27 +2012,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112727875</v>
+        <v>112722755</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2119,19 +2053,20 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596354</v>
+        <v>596576</v>
       </c>
       <c r="R15" t="n">
-        <v>7050376</v>
+        <v>7050419</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2158,9 +2093,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2175,27 +2120,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112724345</v>
+        <v>112722863</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2224,14 +2164,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596420</v>
+        <v>596607</v>
       </c>
       <c r="R16" t="n">
-        <v>7050329</v>
+        <v>7050417</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2263,7 +2203,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2213,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,27 +2228,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112722641</v>
+        <v>112723129</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,14 +2272,14 @@
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596550</v>
+        <v>596624</v>
       </c>
       <c r="R17" t="n">
-        <v>7050492</v>
+        <v>7050371</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2376,7 +2311,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2386,7 +2321,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,27 +2336,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112727885</v>
+        <v>112723545</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2447,19 +2377,20 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596403</v>
+        <v>596620</v>
       </c>
       <c r="R18" t="n">
-        <v>7050522</v>
+        <v>7050392</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2486,9 +2417,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,65 +2444,61 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112727867</v>
+        <v>112724345</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596631</v>
+        <v>596420</v>
       </c>
       <c r="R19" t="n">
-        <v>7050393</v>
+        <v>7050329</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2588,9 +2525,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,65 +2552,61 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112727866</v>
+        <v>112724434</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596449</v>
+        <v>596381</v>
       </c>
       <c r="R20" t="n">
-        <v>7050335</v>
+        <v>7050352</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2690,9 +2633,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2707,65 +2660,61 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112728863</v>
+        <v>112724707</v>
       </c>
       <c r="B21" t="n">
-        <v>90460</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storhammartjärn, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596368</v>
+        <v>596489</v>
       </c>
       <c r="R21" t="n">
-        <v>7050435</v>
+        <v>7050452</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2792,9 +2741,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2809,70 +2768,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112722975</v>
+        <v>112727874</v>
       </c>
       <c r="B22" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596624</v>
+        <v>596435</v>
       </c>
       <c r="R22" t="n">
-        <v>7050408</v>
+        <v>7050440</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2899,19 +2848,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2926,70 +2865,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112722449</v>
+        <v>112727875</v>
       </c>
       <c r="B23" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596495</v>
+        <v>596354</v>
       </c>
       <c r="R23" t="n">
-        <v>7050468</v>
+        <v>7050376</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3016,19 +2945,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3043,27 +2962,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112727879</v>
+        <v>112727876</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3095,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596627</v>
+        <v>596457</v>
       </c>
       <c r="R24" t="n">
-        <v>7050433</v>
+        <v>7050321</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3157,50 +3071,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112728851</v>
+        <v>112727878</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Storhammartjärn, Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596559</v>
+        <v>596631</v>
       </c>
       <c r="R25" t="n">
-        <v>7050319</v>
+        <v>7050393</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3247,27 +3156,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112727882</v>
+        <v>112727879</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3293,19 +3197,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596490</v>
+        <v>596626</v>
       </c>
       <c r="R26" t="n">
-        <v>7050483</v>
+        <v>7050433</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3346,19 +3247,8 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>björk</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>björk</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3375,58 +3265,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112724402</v>
+        <v>112727880</v>
       </c>
       <c r="B27" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>596391</v>
+        <v>596564</v>
       </c>
       <c r="R27" t="n">
-        <v>7050359</v>
+        <v>7050439</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3453,19 +3333,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3480,70 +3350,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112724462</v>
+        <v>112727881</v>
       </c>
       <c r="B28" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596361</v>
+        <v>596547</v>
       </c>
       <c r="R28" t="n">
-        <v>7050372</v>
+        <v>7050464</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3570,19 +3430,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,70 +3447,63 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112723015</v>
+        <v>112727882</v>
       </c>
       <c r="B29" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596603</v>
+        <v>596490</v>
       </c>
       <c r="R29" t="n">
-        <v>7050394</v>
+        <v>7050483</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3687,97 +3530,88 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>björk</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>björk</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112722079</v>
+        <v>112727883</v>
       </c>
       <c r="B30" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596404</v>
+        <v>596466</v>
       </c>
       <c r="R30" t="n">
-        <v>7050493</v>
+        <v>7050481</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3804,19 +3638,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3831,66 +3655,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112727892</v>
+        <v>112727884</v>
       </c>
       <c r="B31" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596356</v>
+        <v>596432</v>
       </c>
       <c r="R31" t="n">
-        <v>7050451</v>
+        <v>7050492</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3949,54 +3764,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112727888</v>
+        <v>112727885</v>
       </c>
       <c r="B32" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596506</v>
+        <v>596404</v>
       </c>
       <c r="R32" t="n">
-        <v>7050289</v>
+        <v>7050522</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4055,58 +3861,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112721852</v>
+        <v>112728852</v>
       </c>
       <c r="B33" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Storhammartjärn, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>596357</v>
+        <v>596369</v>
       </c>
       <c r="R33" t="n">
-        <v>7050425</v>
+        <v>7050350</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4133,97 +3929,93 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112723320</v>
+        <v>112728853</v>
       </c>
       <c r="B34" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Storhammartjärn, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>596616</v>
+        <v>596338</v>
       </c>
       <c r="R34" t="n">
-        <v>7050377</v>
+        <v>7050465</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4250,54 +4042,55 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112722480</v>
+        <v>112728854</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4323,20 +4116,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Storhammartjärn, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>596497</v>
+        <v>596337</v>
       </c>
       <c r="R35" t="n">
-        <v>7050530</v>
+        <v>7050376</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4363,19 +4155,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4390,27 +4172,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112727880</v>
+        <v>112728855</v>
       </c>
       <c r="B36" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4438,14 +4215,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Storhammartjärn, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>596563</v>
+        <v>596542</v>
       </c>
       <c r="R36" t="n">
-        <v>7050439</v>
+        <v>7050247</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4492,49 +4269,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112728864</v>
+        <v>112728856</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4544,10 +4316,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>596332</v>
+        <v>596626</v>
       </c>
       <c r="R37" t="n">
-        <v>7050464</v>
+        <v>7050386</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4606,50 +4378,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112727873</v>
+        <v>112728857</v>
       </c>
       <c r="B38" t="n">
-        <v>79069</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Storhammartjärn, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>596265</v>
+        <v>596641</v>
       </c>
       <c r="R38" t="n">
-        <v>7050426</v>
+        <v>7050413</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4696,66 +4463,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112727886</v>
+        <v>112728858</v>
       </c>
       <c r="B39" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Storhammartjärn, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>596433</v>
+        <v>596607</v>
       </c>
       <c r="R39" t="n">
-        <v>7050341</v>
+        <v>7050421</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4802,70 +4560,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112723167</v>
+        <v>112728859</v>
       </c>
       <c r="B40" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Storhammartjärn, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>596620</v>
+        <v>596345</v>
       </c>
       <c r="R40" t="n">
-        <v>7050372</v>
+        <v>7050466</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4892,19 +4640,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4919,70 +4657,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112722281</v>
+        <v>112728860</v>
       </c>
       <c r="B41" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Storhammartjärn, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>596446</v>
+        <v>596346</v>
       </c>
       <c r="R41" t="n">
-        <v>7050502</v>
+        <v>7050460</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5009,19 +4737,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:52</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5036,66 +4754,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112727890</v>
+        <v>112727873</v>
       </c>
       <c r="B42" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>596471</v>
+        <v>596265</v>
       </c>
       <c r="R42" t="n">
-        <v>7050486</v>
+        <v>7050426</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5154,58 +4863,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112725003</v>
+        <v>112727866</v>
       </c>
       <c r="B43" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>596342</v>
+        <v>596449</v>
       </c>
       <c r="R43" t="n">
-        <v>7050457</v>
+        <v>7050336</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5232,19 +4931,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:36</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5259,71 +4948,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112724108</v>
+        <v>112727867</v>
       </c>
       <c r="B44" t="n">
-        <v>56745</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>596504</v>
+        <v>596631</v>
       </c>
       <c r="R44" t="n">
-        <v>7050285</v>
+        <v>7050393</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5350,19 +5028,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5377,67 +5045,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112727870</v>
+        <v>112727868</v>
       </c>
       <c r="B45" t="n">
-        <v>56761</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>596283</v>
+        <v>596466</v>
       </c>
       <c r="R45" t="n">
-        <v>7050426</v>
+        <v>7050481</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5496,50 +5154,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112728852</v>
+        <v>112727869</v>
       </c>
       <c r="B46" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storhammartjärn, Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>596369</v>
+        <v>596440</v>
       </c>
       <c r="R46" t="n">
-        <v>7050349</v>
+        <v>7050474</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5580,88 +5233,66 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112722575</v>
+        <v>112728851</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Storhammartjärn, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>596529</v>
+        <v>596559</v>
       </c>
       <c r="R47" t="n">
-        <v>7050493</v>
+        <v>7050319</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5688,19 +5319,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5715,66 +5336,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112727891</v>
+        <v>112727899</v>
       </c>
       <c r="B48" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>596440</v>
+        <v>596631</v>
       </c>
       <c r="R48" t="n">
-        <v>7050474</v>
+        <v>7050393</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5833,58 +5445,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112721813</v>
+        <v>112727900</v>
       </c>
       <c r="B49" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>596345</v>
+        <v>596564</v>
       </c>
       <c r="R49" t="n">
-        <v>7050405</v>
+        <v>7050439</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5911,19 +5513,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5938,70 +5530,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112724356</v>
+        <v>112728864</v>
       </c>
       <c r="B50" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Storhammartjärn, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>596420</v>
+        <v>596332</v>
       </c>
       <c r="R50" t="n">
-        <v>7050329</v>
+        <v>7050464</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6028,19 +5610,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6055,62 +5627,62 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112728853</v>
+        <v>112727870</v>
       </c>
       <c r="B51" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storhammartjärn, Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>596338</v>
+        <v>596283</v>
       </c>
       <c r="R51" t="n">
-        <v>7050465</v>
+        <v>7050426</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6151,49 +5723,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112727869</v>
+        <v>112727871</v>
       </c>
       <c r="B52" t="n">
-        <v>79070</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6201,34 +5752,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>596440</v>
+        <v>596547</v>
       </c>
       <c r="R52" t="n">
-        <v>7050474</v>
+        <v>7050464</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6287,15 +5843,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112727874</v>
+        <v>112722234</v>
       </c>
       <c r="B53" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6303,37 +5854,43 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>596434</v>
+        <v>596475</v>
       </c>
       <c r="R53" t="n">
-        <v>7050440</v>
+        <v>7050527</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6360,9 +5917,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6377,27 +5944,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112728857</v>
+        <v>112724108</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,37 +5967,43 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storhammartjärn, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>596641</v>
+        <v>596504</v>
       </c>
       <c r="R54" t="n">
-        <v>7050413</v>
+        <v>7050285</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6462,9 +6030,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6479,63 +6057,62 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112722755</v>
+        <v>112721573</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>596576</v>
+        <v>596325</v>
       </c>
       <c r="R55" t="n">
-        <v>7050419</v>
+        <v>7050427</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6567,7 +6144,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6577,7 +6154,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6604,51 +6181,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112723129</v>
+        <v>112721594</v>
       </c>
       <c r="B56" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>596624</v>
+        <v>596332</v>
       </c>
       <c r="R56" t="n">
-        <v>7050371</v>
+        <v>7050351</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6680,7 +6256,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6690,7 +6266,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6717,53 +6293,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112727883</v>
+        <v>112721813</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>596466</v>
+        <v>596345</v>
       </c>
       <c r="R57" t="n">
-        <v>7050481</v>
+        <v>7050405</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6790,9 +6366,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6807,63 +6393,62 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112721501</v>
+        <v>112721816</v>
       </c>
       <c r="B58" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>596275</v>
+        <v>596388</v>
       </c>
       <c r="R58" t="n">
-        <v>7050381</v>
+        <v>7050400</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6895,7 +6480,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6905,7 +6490,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6932,15 +6517,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112723012</v>
+        <v>112721852</v>
       </c>
       <c r="B59" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6967,20 +6547,20 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>596625</v>
+        <v>596357</v>
       </c>
       <c r="R59" t="n">
-        <v>7050411</v>
+        <v>7050425</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7012,7 +6592,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7022,7 +6602,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7037,63 +6617,62 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>112722495</v>
+        <v>112721962</v>
       </c>
       <c r="B60" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>596516</v>
+        <v>596369</v>
       </c>
       <c r="R60" t="n">
-        <v>7050477</v>
+        <v>7050474</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7125,7 +6704,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7135,7 +6714,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7150,65 +6729,65 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112727896</v>
+        <v>112721987</v>
       </c>
       <c r="B61" t="n">
-        <v>77980</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>596520</v>
+        <v>596375</v>
       </c>
       <c r="R61" t="n">
-        <v>7050457</v>
+        <v>7050477</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7235,9 +6814,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7252,27 +6841,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112721594</v>
+        <v>112722007</v>
       </c>
       <c r="B62" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7299,20 +6883,20 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>596333</v>
+        <v>596370</v>
       </c>
       <c r="R62" t="n">
-        <v>7050351</v>
+        <v>7050476</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7344,7 +6928,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7354,7 +6938,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7381,51 +6965,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112722311</v>
+        <v>112722054</v>
       </c>
       <c r="B63" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>596459</v>
+        <v>596385</v>
       </c>
       <c r="R63" t="n">
-        <v>7050506</v>
+        <v>7050482</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7457,7 +7040,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7467,7 +7050,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7482,65 +7065,65 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112728856</v>
+        <v>112722079</v>
       </c>
       <c r="B64" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storhammartjärn, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>596626</v>
+        <v>596404</v>
       </c>
       <c r="R64" t="n">
-        <v>7050386</v>
+        <v>7050493</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7567,9 +7150,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7584,65 +7177,65 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112727868</v>
+        <v>112722281</v>
       </c>
       <c r="B65" t="n">
-        <v>79070</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>596466</v>
+        <v>596445</v>
       </c>
       <c r="R65" t="n">
-        <v>7050481</v>
+        <v>7050502</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7669,9 +7262,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7686,65 +7289,65 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112728858</v>
+        <v>112722394</v>
       </c>
       <c r="B66" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Storhammartjärn, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>596607</v>
+        <v>596451</v>
       </c>
       <c r="R66" t="n">
-        <v>7050420</v>
+        <v>7050487</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7771,9 +7374,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7788,27 +7401,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112724359</v>
+        <v>112722414</v>
       </c>
       <c r="B67" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7835,20 +7443,20 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>200</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>596442</v>
+        <v>596475</v>
       </c>
       <c r="R67" t="n">
-        <v>7050374</v>
+        <v>7050527</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7880,7 +7488,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7890,7 +7498,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7905,65 +7513,65 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112727895</v>
+        <v>112722449</v>
       </c>
       <c r="B68" t="n">
-        <v>77980</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>596598</v>
+        <v>596495</v>
       </c>
       <c r="R68" t="n">
-        <v>7050432</v>
+        <v>7050468</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7990,9 +7598,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8007,65 +7625,65 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112727881</v>
+        <v>112722561</v>
       </c>
       <c r="B69" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>596547</v>
+        <v>596526</v>
       </c>
       <c r="R69" t="n">
-        <v>7050464</v>
+        <v>7050481</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8092,9 +7710,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8109,27 +7737,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>112727887</v>
+        <v>112722975</v>
       </c>
       <c r="B70" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8156,22 +7779,23 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>596443</v>
+        <v>596624</v>
       </c>
       <c r="R70" t="n">
-        <v>7050333</v>
+        <v>7050408</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8198,9 +7822,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8215,27 +7849,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112724820</v>
+        <v>112723012</v>
       </c>
       <c r="B71" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8262,20 +7891,20 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>900</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>596508</v>
+        <v>596625</v>
       </c>
       <c r="R71" t="n">
-        <v>7050468</v>
+        <v>7050411</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8307,7 +7936,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8317,7 +7946,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8344,15 +7973,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>112722561</v>
+        <v>112723015</v>
       </c>
       <c r="B72" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8379,20 +8003,20 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>596526</v>
+        <v>596603</v>
       </c>
       <c r="R72" t="n">
-        <v>7050480</v>
+        <v>7050394</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8424,7 +8048,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8434,7 +8058,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8461,15 +8085,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>112721573</v>
+        <v>112723167</v>
       </c>
       <c r="B73" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8496,20 +8115,20 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>596325</v>
+        <v>596620</v>
       </c>
       <c r="R73" t="n">
-        <v>7050427</v>
+        <v>7050372</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8541,7 +8160,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8551,7 +8170,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8566,63 +8185,62 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>112724707</v>
+        <v>112723320</v>
       </c>
       <c r="B74" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>596489</v>
+        <v>596616</v>
       </c>
       <c r="R74" t="n">
-        <v>7050452</v>
+        <v>7050378</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8654,7 +8272,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8664,7 +8282,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8679,65 +8297,65 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>112727894</v>
+        <v>112723822</v>
       </c>
       <c r="B75" t="n">
-        <v>77980</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>596428</v>
+        <v>596600</v>
       </c>
       <c r="R75" t="n">
-        <v>7050348</v>
+        <v>7050366</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8764,9 +8382,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8781,65 +8409,65 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>112727897</v>
+        <v>112723983</v>
       </c>
       <c r="B76" t="n">
-        <v>77980</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>596283</v>
+        <v>596579</v>
       </c>
       <c r="R76" t="n">
-        <v>7050426</v>
+        <v>7050326</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8866,9 +8494,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8883,63 +8521,62 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>112724434</v>
+        <v>112724069</v>
       </c>
       <c r="B77" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>596382</v>
+        <v>596460</v>
       </c>
       <c r="R77" t="n">
-        <v>7050352</v>
+        <v>7050313</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8971,7 +8608,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8981,7 +8618,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9008,51 +8645,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>112722863</v>
+        <v>112724356</v>
       </c>
       <c r="B78" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>596607</v>
+        <v>596420</v>
       </c>
       <c r="R78" t="n">
-        <v>7050416</v>
+        <v>7050329</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9084,7 +8720,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9094,7 +8730,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9109,65 +8745,65 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>112727884</v>
+        <v>112724359</v>
       </c>
       <c r="B79" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>596432</v>
+        <v>596442</v>
       </c>
       <c r="R79" t="n">
-        <v>7050492</v>
+        <v>7050374</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9194,9 +8830,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9211,63 +8857,62 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112722145</v>
+        <v>112724402</v>
       </c>
       <c r="B80" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>596453</v>
+        <v>596391</v>
       </c>
       <c r="R80" t="n">
-        <v>7050541</v>
+        <v>7050359</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9299,7 +8944,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9309,7 +8954,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9324,65 +8969,65 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>112727900</v>
+        <v>112724462</v>
       </c>
       <c r="B81" t="n">
-        <v>79076</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen, Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>596563</v>
+        <v>596361</v>
       </c>
       <c r="R81" t="n">
-        <v>7050439</v>
+        <v>7050372</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9409,9 +9054,19 @@
           <t>2023-10-14</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9426,27 +9081,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>112722007</v>
+        <v>112724613</v>
       </c>
       <c r="B82" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9473,20 +9123,20 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>300</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>596370</v>
+        <v>596416</v>
       </c>
       <c r="R82" t="n">
-        <v>7050476</v>
+        <v>7050386</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9518,7 +9168,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9528,7 +9178,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9555,15 +9205,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>112721987</v>
+        <v>112724687</v>
       </c>
       <c r="B83" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9590,20 +9235,20 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>596375</v>
+        <v>596517</v>
       </c>
       <c r="R83" t="n">
-        <v>7050478</v>
+        <v>7050389</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9635,7 +9280,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9645,7 +9290,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9660,27 +9305,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112724734</v>
+        <v>112724722</v>
       </c>
       <c r="B84" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9707,20 +9347,20 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>596487</v>
+        <v>596494</v>
       </c>
       <c r="R84" t="n">
-        <v>7050449</v>
+        <v>7050406</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9752,7 +9392,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9762,7 +9402,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9777,27 +9417,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112722414</v>
+        <v>112724734</v>
       </c>
       <c r="B85" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9824,20 +9459,20 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>500</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>596475</v>
+        <v>596487</v>
       </c>
       <c r="R85" t="n">
-        <v>7050528</v>
+        <v>7050449</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9869,7 +9504,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9879,7 +9514,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9906,56 +9541,50 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112722234</v>
+        <v>112724820</v>
       </c>
       <c r="B86" t="n">
-        <v>56745</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>596475</v>
+        <v>596508</v>
       </c>
       <c r="R86" t="n">
-        <v>7050528</v>
+        <v>7050468</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9987,7 +9616,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9997,7 +9626,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10024,15 +9653,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112724687</v>
+        <v>112725003</v>
       </c>
       <c r="B87" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10059,20 +9683,20 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>300</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>596517</v>
+        <v>596342</v>
       </c>
       <c r="R87" t="n">
-        <v>7050388</v>
+        <v>7050457</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10104,7 +9728,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10114,7 +9738,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10129,27 +9753,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112721962</v>
+        <v>112727886</v>
       </c>
       <c r="B88" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10176,23 +9795,22 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>596369</v>
+        <v>596433</v>
       </c>
       <c r="R88" t="n">
-        <v>7050473</v>
+        <v>7050341</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10219,19 +9837,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10246,27 +9854,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>112727893</v>
+        <v>112727887</v>
       </c>
       <c r="B89" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10293,7 +9896,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10302,10 +9905,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>596364</v>
+        <v>596443</v>
       </c>
       <c r="R89" t="n">
-        <v>7050450</v>
+        <v>7050334</v>
       </c>
       <c r="S89" t="n">
         <v>20</v>
@@ -10364,54 +9967,52 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>112723545</v>
+        <v>112727888</v>
       </c>
       <c r="B90" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>596620</v>
+        <v>596507</v>
       </c>
       <c r="R90" t="n">
-        <v>7050393</v>
+        <v>7050289</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10438,19 +10039,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10465,62 +10056,61 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>112727878</v>
+        <v>112727889</v>
       </c>
       <c r="B91" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>596631</v>
+        <v>596559</v>
       </c>
       <c r="R91" t="n">
-        <v>7050393</v>
+        <v>7050308</v>
       </c>
       <c r="S91" t="n">
         <v>20</v>
@@ -10579,15 +10169,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112722394</v>
+        <v>112727890</v>
       </c>
       <c r="B92" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10614,23 +10199,22 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>596451</v>
+        <v>596471</v>
       </c>
       <c r="R92" t="n">
-        <v>7050487</v>
+        <v>7050486</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10657,19 +10241,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10684,27 +10258,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>112723983</v>
+        <v>112727891</v>
       </c>
       <c r="B93" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10731,23 +10300,22 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>596579</v>
+        <v>596440</v>
       </c>
       <c r="R93" t="n">
-        <v>7050326</v>
+        <v>7050474</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10774,19 +10342,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>15:55</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10801,27 +10359,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>112722054</v>
+        <v>112727892</v>
       </c>
       <c r="B94" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10848,23 +10401,22 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>596385</v>
+        <v>596357</v>
       </c>
       <c r="R94" t="n">
-        <v>7050483</v>
+        <v>7050451</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10891,19 +10443,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:41</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10918,62 +10460,61 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>112728860</v>
+        <v>112727893</v>
       </c>
       <c r="B95" t="n">
-        <v>79043</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Storhammartjärn, Ång</t>
+          <t>Stor-Hammartjärnen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>596346</v>
+        <v>596363</v>
       </c>
       <c r="R95" t="n">
-        <v>7050460</v>
+        <v>7050449</v>
       </c>
       <c r="S95" t="n">
         <v>20</v>
@@ -11020,27 +10561,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Malin Norrby</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>112724613</v>
+        <v>112728862</v>
       </c>
       <c r="B96" t="n">
-        <v>97127</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11067,23 +10603,22 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stor-Hammartjärnen (Stor-Hammartjärnen), Ång</t>
+          <t>Storhammartjärn, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>596416</v>
+        <v>596362</v>
       </c>
       <c r="R96" t="n">
-        <v>7050386</v>
+        <v>7050461</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11110,19 +10645,9 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2023-10-14</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11137,15 +10662,112 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Malin Norrby</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>112727872</v>
+      </c>
+      <c r="B97" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Stor-Hammartjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>596466</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7050465</v>
+      </c>
+      <c r="S97" t="n">
+        <v>20</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
